--- a/Assessment Questions/CDE/Big Data Advance/KAFKA and Spark/Configuring Kafka cluster/Configuring_Kafka_Cluster.xlsx
+++ b/Assessment Questions/CDE/Big Data Advance/KAFKA and Spark/Configuring Kafka cluster/Configuring_Kafka_Cluster.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Configuring Kafka Cluster" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -439,7 +439,7 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Answer</t>
+          <t>Question Type</t>
         </is>
       </c>
     </row>
@@ -466,7 +466,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>C) 3</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -486,10 +486,9 @@
           <t>What configuration property sets the directory for Kafka data storage?</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>log.dirs</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -516,7 +515,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>A) broker.rack</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -536,10 +535,9 @@
           <t>A cluster needs to handle 100 MB/s write throughput. Each broker has 10 MB/s disk write capacity. How many brokers are needed minimum?</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>10 brokers minimum</t>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
@@ -559,10 +557,9 @@
           <t>What configuration controls the maximum size of a message the broker will accept?</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>max.message.bytes</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -589,7 +586,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>A) num.network.threads</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -609,10 +606,9 @@
           <t>What configuration defines how long a broker waits for replicas to acknowledge a write?</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>replica.lag.time.max.ms</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -632,10 +628,9 @@
           <t>You need to configure a topic with 24 partitions for a 6-node cluster. What's a recommended partition distribution strategy?</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>4 partitions per broker (24/6)</t>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
@@ -662,7 +657,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>B) Default for topics created without specifying replication</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -682,10 +677,9 @@
           <t>What configuration controls the maximum number of partitions per broker?</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>num.partitions (or max.partitions.per.broker)</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -712,7 +706,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>B) 1-4 GB</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -732,10 +726,9 @@
           <t>A Kafka cluster is experiencing high disk usage. What configuration would you adjust to reduce storage?</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Reduce retention.ms or retention.bytes</t>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
@@ -755,10 +748,9 @@
           <t>What is the configuration to enable TLS/SSL encryption?</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ssl.keystore.location and ssl.truststore.location</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -785,7 +777,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>B) Only ISR replicas can become leader</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -805,10 +797,9 @@
           <t>What configuration controls the number of partitions for a new topic?</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>num.partitions</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -828,10 +819,9 @@
           <t>A broker fails to start because "log directory is already in use." What is the likely cause?</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Another broker instance using the same log.dirs</t>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
@@ -858,7 +848,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>B) Clients to connect to brokers</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -878,10 +868,9 @@
           <t>What configuration sets the minimum number of replicas for a successful write?</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>min.insync.replicas</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -908,7 +897,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>C) heap size and off-heap</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -928,10 +917,9 @@
           <t>You need to increase the retention period from 7 days to 30 days for an existing topic. What do you need to do?</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Alter the topic configuration: retention.ms=2592000000</t>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
